--- a/Задание/ПУ/Модуль 1/import/Заказ_import.xlsx
+++ b/Задание/ПУ/Модуль 1/import/Заказ_import.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\st53\Desktop\Прил_ОЗ_КОД 09.02.07-2-2026\ПУ\Модуль 1\Прил_2_ОЗ_КОД 09.02.07-2-2026-М1\import\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Новая папка (2)\Пример\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,12 +30,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
+  <si>
+    <t>Номер заказа</t>
+  </si>
+  <si>
+    <t>Дата заказа</t>
+  </si>
+  <si>
+    <t>Дата доставки</t>
+  </si>
+  <si>
+    <t>Код для получения</t>
+  </si>
+  <si>
+    <t>Статус заказа</t>
+  </si>
   <si>
     <t xml:space="preserve">Новый </t>
   </si>
   <si>
     <t>Завершен</t>
+  </si>
+  <si>
+    <t>Сазонов Руслан Германович</t>
+  </si>
+  <si>
+    <t>Одинцов Серафим Артёмович</t>
+  </si>
+  <si>
+    <t>Степанов Михаил Артёмович</t>
+  </si>
+  <si>
+    <t>Никифорова Весения Николаевна</t>
+  </si>
+  <si>
+    <t>ФИО авторизированного клиента</t>
+  </si>
+  <si>
+    <t>Артикул заказа</t>
+  </si>
+  <si>
+    <t>Адрес пункта выдачи</t>
   </si>
   <si>
     <t>А112Т4, 2, F635R4, 2</t>
@@ -63,10 +99,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
-  </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -76,6 +109,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times Roman"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times Roman"/>
@@ -124,9 +164,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -136,14 +179,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -458,44 +499,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
+  <dimension ref="A1:L54"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="2" max="2" width="30.25" customWidth="1"/>
-    <col min="3" max="3" width="21.75" style="8" customWidth="1"/>
-    <col min="4" max="4" width="10.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.25" customWidth="1"/>
-    <col min="6" max="6" width="32.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.25" customWidth="1"/>
-    <col min="8" max="8" width="22.25" customWidth="1"/>
+    <col min="2" max="2" width="30.19921875" customWidth="1"/>
+    <col min="3" max="3" width="21.69921875" customWidth="1"/>
+    <col min="4" max="4" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.296875" customWidth="1"/>
+    <col min="6" max="6" width="32.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.19921875" customWidth="1"/>
+    <col min="8" max="8" width="22.296875" customWidth="1"/>
     <col min="11" max="11" width="35" customWidth="1"/>
     <col min="12" max="12" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="2">
+    <row r="1" spans="1:12" ht="31.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6">
-        <v>45715</v>
-      </c>
-      <c r="D1" s="6">
-        <v>45767</v>
-      </c>
-      <c r="E1" s="2">
-        <v>1</v>
-      </c>
-      <c r="F1" s="5">
+      <c r="E1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="G1" s="2">
-        <v>901</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>1</v>
       </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -503,59 +544,59 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="6">
+        <v>45715</v>
+      </c>
+      <c r="D2" s="6">
+        <v>45767</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3">
+        <v>901</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="6">
+      <c r="B3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="6">
         <v>44832</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D3" s="6">
         <v>45768</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E3" s="5">
         <v>11</v>
       </c>
-      <c r="F2" s="5">
-        <v>1</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="F3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5">
         <v>902</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="4">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="6">
-        <v>45737</v>
-      </c>
-      <c r="D3" s="6">
-        <v>45769</v>
-      </c>
-      <c r="E3" s="2">
-        <v>2</v>
-      </c>
-      <c r="F3" s="5">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2">
-        <v>903</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>1</v>
+      <c r="H3" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -563,29 +604,29 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>5</v>
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C4" s="6">
-        <v>45708</v>
+        <v>45737</v>
       </c>
       <c r="D4" s="6">
-        <v>45770</v>
-      </c>
-      <c r="E4" s="4">
-        <v>11</v>
-      </c>
-      <c r="F4" s="5">
-        <v>3</v>
-      </c>
-      <c r="G4" s="4">
-        <v>904</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>1</v>
+        <v>45769</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="3">
+        <v>903</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -593,29 +634,29 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="4">
-        <v>5</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>2</v>
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C5" s="6">
-        <v>45733</v>
+        <v>45708</v>
       </c>
       <c r="D5" s="6">
-        <v>45771</v>
-      </c>
-      <c r="E5" s="2">
-        <v>2</v>
-      </c>
-      <c r="F5" s="5">
-        <v>4</v>
-      </c>
-      <c r="G5" s="2">
-        <v>905</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>1</v>
+        <v>45770</v>
+      </c>
+      <c r="E5" s="5">
+        <v>11</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="5">
+        <v>904</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -623,29 +664,29 @@
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="4">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="6">
+        <v>45733</v>
+      </c>
+      <c r="D6" s="6">
+        <v>45771</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="3">
+        <v>905</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="6">
-        <v>45717</v>
-      </c>
-      <c r="D6" s="6">
-        <v>45772</v>
-      </c>
-      <c r="E6" s="4">
-        <v>15</v>
-      </c>
-      <c r="F6" s="5">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4">
-        <v>906</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>1</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -653,29 +694,29 @@
       <c r="L6" s="1"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="4">
-        <v>7</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>8</v>
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="6">
+        <v>45717</v>
       </c>
       <c r="D7" s="6">
-        <v>45773</v>
-      </c>
-      <c r="E7" s="2">
-        <v>3</v>
-      </c>
-      <c r="F7" s="5">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2">
-        <v>907</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>1</v>
+        <v>45772</v>
+      </c>
+      <c r="E7" s="5">
+        <v>15</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="5">
+        <v>906</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -683,29 +724,29 @@
       <c r="L7" s="1"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="4">
-        <v>8</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="6">
-        <v>45747</v>
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="D8" s="6">
-        <v>45774</v>
-      </c>
-      <c r="E8" s="4">
-        <v>19</v>
-      </c>
-      <c r="F8" s="5">
+        <v>45773</v>
+      </c>
+      <c r="E8" s="3">
         <v>3</v>
       </c>
-      <c r="G8" s="4">
-        <v>908</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>0</v>
+      <c r="F8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="3">
+        <v>907</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -713,29 +754,29 @@
       <c r="L8" s="1"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="4">
-        <v>9</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>6</v>
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C9" s="6">
-        <v>45749</v>
+        <v>45747</v>
       </c>
       <c r="D9" s="6">
-        <v>45775</v>
-      </c>
-      <c r="E9" s="2">
+        <v>45774</v>
+      </c>
+      <c r="E9" s="5">
+        <v>19</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="5">
+        <v>908</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>5</v>
-      </c>
-      <c r="F9" s="5">
-        <v>4</v>
-      </c>
-      <c r="G9" s="2">
-        <v>909</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>0</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -743,29 +784,29 @@
       <c r="L9" s="1"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="4">
-        <v>10</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>7</v>
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C10" s="6">
-        <v>45750</v>
+        <v>45749</v>
       </c>
       <c r="D10" s="6">
-        <v>45776</v>
-      </c>
-      <c r="E10" s="4">
-        <v>19</v>
-      </c>
-      <c r="F10" s="5">
-        <v>4</v>
-      </c>
-      <c r="G10" s="4">
-        <v>910</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>0</v>
+        <v>45775</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="3">
+        <v>909</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -773,14 +814,30 @@
       <c r="L10" s="1"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="6">
+        <v>45750</v>
+      </c>
+      <c r="D11" s="6">
+        <v>45776</v>
+      </c>
+      <c r="E11" s="5">
+        <v>19</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="5">
+        <v>910</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>5</v>
+      </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -788,11 +845,11 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="B12" s="4"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="F12" s="3"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -817,8 +874,8 @@
     <row r="14" spans="1:12">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -830,9 +887,9 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="1"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -844,9 +901,9 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="1"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -858,9 +915,9 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="1"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -872,9 +929,9 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="1"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -886,9 +943,9 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="1"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -900,9 +957,9 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -915,8 +972,8 @@
     <row r="21" spans="1:12">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -929,8 +986,8 @@
     <row r="22" spans="1:12">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -943,8 +1000,8 @@
     <row r="23" spans="1:12">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -957,8 +1014,8 @@
     <row r="24" spans="1:12">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -971,8 +1028,8 @@
     <row r="25" spans="1:12">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -985,8 +1042,8 @@
     <row r="26" spans="1:12">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -999,8 +1056,8 @@
     <row r="27" spans="1:12">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -1013,8 +1070,8 @@
     <row r="28" spans="1:12">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -1027,8 +1084,8 @@
     <row r="29" spans="1:12">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -1041,8 +1098,8 @@
     <row r="30" spans="1:12">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -1055,8 +1112,8 @@
     <row r="31" spans="1:12">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -1069,8 +1126,8 @@
     <row r="32" spans="1:12">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -1083,8 +1140,8 @@
     <row r="33" spans="1:12">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -1097,8 +1154,8 @@
     <row r="34" spans="1:12">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -1111,8 +1168,8 @@
     <row r="35" spans="1:12">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -1125,8 +1182,8 @@
     <row r="36" spans="1:12">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -1139,8 +1196,8 @@
     <row r="37" spans="1:12">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -1153,8 +1210,8 @@
     <row r="38" spans="1:12">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -1167,8 +1224,8 @@
     <row r="39" spans="1:12">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -1181,8 +1238,8 @@
     <row r="40" spans="1:12">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -1195,8 +1252,8 @@
     <row r="41" spans="1:12">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -1209,8 +1266,8 @@
     <row r="42" spans="1:12">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -1223,8 +1280,8 @@
     <row r="43" spans="1:12">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -1237,8 +1294,8 @@
     <row r="44" spans="1:12">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -1251,8 +1308,8 @@
     <row r="45" spans="1:12">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -1265,8 +1322,8 @@
     <row r="46" spans="1:12">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -1279,8 +1336,8 @@
     <row r="47" spans="1:12">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -1293,8 +1350,8 @@
     <row r="48" spans="1:12">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -1307,8 +1364,8 @@
     <row r="49" spans="1:12">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -1321,8 +1378,8 @@
     <row r="50" spans="1:12">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -1335,8 +1392,8 @@
     <row r="51" spans="1:12">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -1349,8 +1406,8 @@
     <row r="52" spans="1:12">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -1363,8 +1420,8 @@
     <row r="53" spans="1:12">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -1374,6 +1431,20 @@
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
     </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
